--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 17:04</t>
+          <t>更新时间: 2026-10-21 21:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-21 21:33</t>
+          <t>更新时间: 2026-10-22 09:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 09:57</t>
+          <t>更新时间: 2026-10-22 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 12:40</t>
+          <t>更新时间: 2026-10-22 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 13:49</t>
+          <t>更新时间: 2026-10-22 15:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 15:44</t>
+          <t>更新时间: 2026-10-22 16:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 16:57</t>
+          <t>更新时间: 2026-10-23 10:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 10:03</t>
+          <t>更新时间: 2026-10-23 12:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 12:46</t>
+          <t>更新时间: 2026-10-23 13:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 13:48</t>
+          <t>更新时间: 2026-10-23 15:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 15:42</t>
+          <t>更新时间: 2026-10-23 16:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 16:52</t>
+          <t>更新时间: 2026-10-24 10:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 10:07</t>
+          <t>更新时间: 2026-10-24 12:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 12:33</t>
+          <t>更新时间: 2026-10-24 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 13:28</t>
+          <t>更新时间: 2026-10-24 15:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 15:25</t>
+          <t>更新时间: 2026-10-24 16:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 16:26</t>
+          <t>更新时间: 2026-10-25 09:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 09:45</t>
+          <t>更新时间: 2026-10-25 12:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 12:37</t>
+          <t>更新时间: 2026-10-25 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 13:46</t>
+          <t>更新时间: 2026-10-25 15:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 15:40</t>
+          <t>更新时间: 2026-10-25 16:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 16:45</t>
+          <t>更新时间: 2026-10-26 09:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 09:46</t>
+          <t>更新时间: 2026-10-26 12:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 12:43</t>
+          <t>更新时间: 2026-10-26 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 13:49</t>
+          <t>更新时间: 2026-10-26 15:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 15:55</t>
+          <t>更新时间: 2026-10-26 17:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-26 17:25</t>
+          <t>更新时间: 2026-10-27 10:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 10:36</t>
+          <t>更新时间: 2026-10-27 13:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 13:00</t>
+          <t>更新时间: 2026-10-27 14:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 14:01</t>
+          <t>更新时间: 2026-10-27 16:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 16:02</t>
+          <t>更新时间: 2026-10-27 17:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 17:23</t>
+          <t>更新时间: 2026-10-28 10:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 10:46</t>
+          <t>更新时间: 2026-10-28 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 13:38</t>
+          <t>更新时间: 2026-10-28 14:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 14:41</t>
+          <t>更新时间: 2026-10-28 16:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 16:43</t>
+          <t>更新时间: 2026-10-28 18:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 18:05</t>
+          <t>更新时间: 2026-10-29 10:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 10:58</t>
+          <t>更新时间: 2026-10-29 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 13:45</t>
+          <t>更新时间: 2026-10-29 14:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 14:48</t>
+          <t>更新时间: 2026-10-29 16:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 16:39</t>
+          <t>更新时间: 2026-10-29 18:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 18:28</t>
+          <t>更新时间: 2026-10-30 11:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 11:05</t>
+          <t>更新时间: 2026-10-30 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 13:43</t>
+          <t>更新时间: 2026-10-30 14:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 14:51</t>
+          <t>更新时间: 2026-10-30 16:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 16:46</t>
+          <t>更新时间: 2026-10-30 18:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 18:29</t>
+          <t>更新时间: 2026-10-31 10:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-31 10:54</t>
+          <t>更新时间: 2026-10-31 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-31 13:36</t>
+          <t>更新时间: 2026-10-31 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-31 14:43</t>
+          <t>更新时间: 2026-10-31 16:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-31 16:33</t>
+          <t>更新时间: 2026-10-31 17:59</t>
         </is>
       </c>
     </row>
